--- a/UC60Plus_N1B_PCB_수량산출.xlsx
+++ b/UC60Plus_N1B_PCB_수량산출.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PCB 수량 산출" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PCB 발주수량 검토" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,13 +60,19 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="00BF8F00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <i val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="00808080"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -91,8 +97,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -124,17 +130,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -143,25 +146,29 @@
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,21 +534,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UC60Plus_N1B  CP Yield 기반 PCB 소요량 산출</t>
+          <t>UC60Plus_N1B  CP Yield별 PCB 소요량 검토</t>
         </is>
       </c>
     </row>
@@ -555,260 +563,359 @@
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1. PCB 재고 현황</t>
+          <t>1. Wafer / Die 기본 정보</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="4" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>PCB Supplier</t>
+          <t>Wafer Qty</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>Die Qty (per wafer)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Total Die Qty</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Mass Production</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>16004</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>1696424</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Total Die Qty</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="10" t="n">
+        <v>1697944</v>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2. CP Yield 시나리오별 FCCSP Input Qty (= PCB 필요수량)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>CP Yield</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Good Die Qty
+(MP)</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Eng. Qty</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>FCCSP Input Qty
+(= 필요 PCB)</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
           <t>PCB 현재고</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>PCB Order 수량</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>PCB 총수량</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>UC60Plus_N1B</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>DDE</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>PCB 추가발주
+필요수량</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>1441960</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1443480</v>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>7287</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F12" s="7" t="n">
+        <v>1436193</v>
+      </c>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>1492853</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1494373</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>7287</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>1487086</v>
+      </c>
+      <c r="G13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>1526781</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>1528301</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>7287</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>1521014</v>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>현재 발주 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>1560710</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>1562230</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>7287</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>1554943</v>
+      </c>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1611602</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1613122</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>7287</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1605835</v>
+      </c>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>3. 현재 PCB 발주 현황 (참고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>PCB 현재고</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="7" t="n">
+        <v>7287</v>
+      </c>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n"/>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>PCB 발주 수량 (CP Yield 90% 기준)</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="7" t="n">
         <v>1600000</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="n"/>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>PCB 총수량 (현재고 + 발주)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="7" t="n">
         <v>1607287</v>
       </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2. Wafer / Die 투입 계획 (CP 예상 Yield 기반)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Wafer Qty</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Die Qty</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>CP 예상 Yield</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>FCCSP Input Qty</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>1520</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>106</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>1696424</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>1526782</v>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Mass Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>투입 총 수량</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="11" t="n">
-        <v>1528302</v>
-      </c>
-      <c r="F12" s="10" t="n"/>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>3. PCB 수량 과부족 분석</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="n"/>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>PCB 총수량 (현재고 + 발주)</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="6" t="n">
-        <v>1607287</v>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="n"/>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>FCCSP 투입 총 수량</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="6" t="n">
-        <v>1528302</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>PCB 여유 수량 (A - B)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="18" t="n">
-        <v>78985</v>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>A - B</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>※ CP 예상 Yield 90% 기준, PCB 여유분 78,985 EA 확보</t>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>[요청 사항]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>CP 예상 Yield를 회신 부탁드리며, 이에 따른 PCB 발주수량 확정 요청드립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>※ 현재 PCB 발주는 CP Yield 90% 예상 기준으로 진행하였으며, 실제 Yield에 따라 발주수량 조정이 필요합니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="B16:D16"/>
+  <mergeCells count="17">
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="1" fitToWidth="1"/>

--- a/UC60Plus_N1B_PCB_수량산출.xlsx
+++ b/UC60Plus_N1B_PCB_수량산출.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,28 +28,7 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="002F5496"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="002F5496"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
     <font>
@@ -59,24 +38,16 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00BF8F00"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00C00000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -87,18 +58,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
         <bgColor rgb="002F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-        <bgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,55 +79,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -534,390 +471,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UC60Plus_N1B  CP Yield별 PCB 소요량 검토</t>
-        </is>
-      </c>
+          <t>Wafer QTY</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Die QTY</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr"/>
+      <c r="D1" s="2" t="inlineStr"/>
+      <c r="E1" s="2" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Date: 2026.06.25</t>
-        </is>
+      <c r="A2" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>1696424</v>
       </c>
     </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>1. Wafer / Die 기본 정보</t>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>CP Yield</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>FCCSP 예상 투입 QTY</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>현 PCB 발주 수량</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>예상 PCB 잔여 수량</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Wafer Qty</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Die Qty (per wafer)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Total Die Qty</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1441961</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>158039</v>
+      </c>
+      <c r="E5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>1520</v>
-      </c>
+      <c r="A6" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1526782</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>73218</v>
+      </c>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Mass Production</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>106</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>16004</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>1696424</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Total Die Qty</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="10" t="n">
-        <v>1697944</v>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2. CP Yield 시나리오별 FCCSP Input Qty (= PCB 필요수량)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>CP Yield</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Good Die Qty
-(MP)</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Eng. Qty</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>FCCSP Input Qty
-(= 필요 PCB)</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>PCB 현재고</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>PCB 추가발주
-필요수량</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>1441960</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>1520</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>1443480</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>7287</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>1436193</v>
-      </c>
-      <c r="G12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>1492853</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>1520</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>1494373</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>7287</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>1487086</v>
-      </c>
-      <c r="G13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>1526781</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>1520</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>1528301</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>7287</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>1521014</v>
-      </c>
-      <c r="G14" s="15" t="inlineStr">
-        <is>
-          <t>현재 발주 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>1560710</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>1520</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>1562230</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>7287</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>1554943</v>
-      </c>
-      <c r="G15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A7" s="5" t="n">
         <v>0.95</v>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>1611602</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>1520</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>1613122</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>7287</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>1605835</v>
-      </c>
-      <c r="G16" s="6" t="n"/>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>3. 현재 PCB 발주 현황 (참고)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>PCB 현재고</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="7" t="n">
-        <v>7287</v>
-      </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>PCB 발주 수량 (CP Yield 90% 기준)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="7" t="n">
+      <c r="B7" s="6" t="n">
+        <v>1611603</v>
+      </c>
+      <c r="C7" s="6" t="n">
         <v>1600000</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>PCB 총수량 (현재고 + 발주)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="7" t="n">
-        <v>1607287</v>
-      </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>[요청 사항]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>CP 예상 Yield를 회신 부탁드리며, 이에 따른 PCB 발주수량 확정 요청드립니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>※ 현재 PCB 발주는 CP Yield 90% 예상 기준으로 진행하였으며, 실제 Yield에 따라 발주수량 조정이 필요합니다.</t>
+      <c r="D7" s="8" t="n">
+        <v>-11603</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>발주필요</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="B20:D20"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>